--- a/artfynd/A 8533-2024 artfynd.xlsx
+++ b/artfynd/A 8533-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62064254</v>
+        <v>81531</v>
       </c>
       <c r="B2" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skorvdalen Vemdalen, Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>448140.2566694526</v>
+        <v>448018</v>
       </c>
       <c r="R2" t="n">
-        <v>6919490.005346244</v>
+        <v>6919536</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +744,14 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Naturinventering av Skorvdalen / Lars-Olof Grund 2007. Skorvdalen, området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +766,7 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -796,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>316128</v>
+        <v>104888</v>
       </c>
       <c r="B3" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,25 +793,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447939.0300337338</v>
+        <v>448546</v>
       </c>
       <c r="R3" t="n">
-        <v>6919360.518062259</v>
+        <v>6919610</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,19 +851,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -922,12 +892,7 @@
         <v>316125</v>
       </c>
       <c r="B4" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447999.6849633505</v>
+        <v>448000</v>
       </c>
       <c r="R4" t="n">
-        <v>6919319.230993751</v>
+        <v>6919319</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,19 +959,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1042,15 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>316133</v>
+        <v>316126</v>
       </c>
       <c r="B5" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,10 +1034,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448501.8469182875</v>
+        <v>447955</v>
       </c>
       <c r="R5" t="n">
-        <v>6919601.258685119</v>
+        <v>6919333</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1117,19 +1067,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1165,15 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>316129</v>
+        <v>316128</v>
       </c>
       <c r="B6" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1207,10 +1142,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447959.4099930978</v>
+        <v>447939</v>
       </c>
       <c r="R6" t="n">
-        <v>6919416.772023014</v>
+        <v>6919361</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1240,19 +1175,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1288,15 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>316138</v>
+        <v>316129</v>
       </c>
       <c r="B7" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448142.5265587351</v>
+        <v>447959</v>
       </c>
       <c r="R7" t="n">
-        <v>6919725.977727721</v>
+        <v>6919417</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1363,19 +1283,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1411,15 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>316136</v>
+        <v>316131</v>
       </c>
       <c r="B8" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1453,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448159.9546597193</v>
+        <v>448219</v>
       </c>
       <c r="R8" t="n">
-        <v>6919682.123589269</v>
+        <v>6919476</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1486,19 +1391,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1534,15 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>316137</v>
+        <v>316132</v>
       </c>
       <c r="B9" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1576,10 +1466,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448195.9006822239</v>
+        <v>448019</v>
       </c>
       <c r="R9" t="n">
-        <v>6919694.548410106</v>
+        <v>6919510</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1609,19 +1499,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1657,15 +1537,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>316132</v>
+        <v>316133</v>
       </c>
       <c r="B10" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1699,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>448018.913196541</v>
+        <v>448502</v>
       </c>
       <c r="R10" t="n">
-        <v>6919510.438457401</v>
+        <v>6919601</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1732,19 +1607,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1780,15 +1645,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>81531</v>
+        <v>316134</v>
       </c>
       <c r="B11" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1796,24 +1656,25 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>864</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1821,10 +1682,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448017.9243851277</v>
+        <v>448279</v>
       </c>
       <c r="R11" t="n">
-        <v>6919536.420005373</v>
+        <v>6919601</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1854,19 +1715,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1902,15 +1753,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>316131</v>
+        <v>316135</v>
       </c>
       <c r="B12" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,10 +1790,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448219.4412799128</v>
+        <v>448034</v>
       </c>
       <c r="R12" t="n">
-        <v>6919475.793947647</v>
+        <v>6919610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,19 +1823,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2025,15 +1861,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>316126</v>
+        <v>316136</v>
       </c>
       <c r="B13" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2067,10 +1898,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447955.317426034</v>
+        <v>448160</v>
       </c>
       <c r="R13" t="n">
-        <v>6919332.905647604</v>
+        <v>6919682</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2100,19 +1931,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2148,15 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>316135</v>
+        <v>316137</v>
       </c>
       <c r="B14" t="n">
-        <v>77588</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2190,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448033.9336934599</v>
+        <v>448196</v>
       </c>
       <c r="R14" t="n">
-        <v>6919610.358875123</v>
+        <v>6919695</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2223,19 +2039,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2271,37 +2077,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1901591</v>
+        <v>316138</v>
       </c>
       <c r="B15" t="n">
-        <v>76862</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6443</v>
+        <v>864</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2313,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448201.629393442</v>
+        <v>448143</v>
       </c>
       <c r="R15" t="n">
-        <v>6919704.660017993</v>
+        <v>6919726</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,19 +2147,9 @@
           <t>2007-07-26</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2007-07-26</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2394,50 +2185,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>115248171</v>
+        <v>62064254</v>
       </c>
       <c r="B16" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Skorvdalen Vemdalen, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>447166</v>
+        <v>448140</v>
       </c>
       <c r="R16" t="n">
-        <v>6918864</v>
+        <v>6919490</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2464,12 +2250,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Naturinventering av Skorvdalen / Lars-Olof Grund 2007. Skorvdalen, området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2484,62 +2275,63 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>115250672</v>
+        <v>811798</v>
       </c>
       <c r="B17" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6464</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447014</v>
+        <v>448279</v>
       </c>
       <c r="R17" t="n">
-        <v>6919303</v>
+        <v>6919601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2566,12 +2358,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,27 +2383,26 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115250589</v>
+        <v>811799</v>
       </c>
       <c r="B18" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2614,34 +2410,36 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447016</v>
+        <v>448546</v>
       </c>
       <c r="R18" t="n">
-        <v>6919258</v>
+        <v>6919610</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2668,12 +2466,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2688,62 +2491,63 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115247963</v>
+        <v>1901591</v>
       </c>
       <c r="B19" t="n">
-        <v>90897</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78685</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>760</v>
+        <v>6443</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447189</v>
+        <v>448202</v>
       </c>
       <c r="R19" t="n">
-        <v>6918832</v>
+        <v>6919705</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2770,12 +2574,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2790,65 +2599,66 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>115248081</v>
+        <v>1887400</v>
       </c>
       <c r="B20" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Skorvdalen, Vemdalen,, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447193</v>
+        <v>448279</v>
       </c>
       <c r="R20" t="n">
-        <v>6918846</v>
+        <v>6919601</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2872,12 +2682,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-26</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråberget,</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2892,27 +2707,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Lars-Olof Grund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>115251041</v>
+        <v>59520431</v>
       </c>
       <c r="B21" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2920,34 +2734,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>229821</v>
+        <v>220075</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Smaldalen (Smaldalen), Hjd</t>
+          <t>Skorvdalen, området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråb, Hjd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>446882</v>
+        <v>448077</v>
       </c>
       <c r="R21" t="n">
-        <v>6919449</v>
+        <v>6919366</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2974,12 +2788,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2994,27 +2808,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lars-Olof Grund</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>115250791</v>
+        <v>59520432</v>
       </c>
       <c r="B22" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101897</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3022,34 +2831,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>229821</v>
+        <v>220075</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gullpudra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chrysosplenium alternifolium</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Smaldalen (Smaldalen), Hjd</t>
+          <t>Skorvdalen, området mellan Rönningsvallen - Gammelnipan - Nipfjället - Gråb, Hjd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>446966</v>
+        <v>448059</v>
       </c>
       <c r="R22" t="n">
-        <v>6919361</v>
+        <v>6919628</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3076,12 +2885,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2007-07-15</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,27 +2905,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Lars-Olof Grund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>115249895</v>
+        <v>115284963</v>
       </c>
       <c r="B23" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3124,34 +2928,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447152</v>
+        <v>447133</v>
       </c>
       <c r="R23" t="n">
-        <v>6918961</v>
+        <v>6919015</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3192,68 +2999,64 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>115251592</v>
+        <v>115247963</v>
       </c>
       <c r="B24" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229821</v>
+        <v>760</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447187</v>
+        <v>447189</v>
       </c>
       <c r="R24" t="n">
-        <v>6918950</v>
+        <v>6918832</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3312,53 +3115,51 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115250834</v>
+        <v>115285005</v>
       </c>
       <c r="B25" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>760</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Smaldalen (Smaldalen), Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>446949</v>
+        <v>447189</v>
       </c>
       <c r="R25" t="n">
-        <v>6919364</v>
+        <v>6918830</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3396,33 +3197,29 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115250401</v>
+        <v>115284871</v>
       </c>
       <c r="B26" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3430,37 +3227,40 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447049</v>
+        <v>446952</v>
       </c>
       <c r="R26" t="n">
-        <v>6919190</v>
+        <v>6919314</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3498,33 +3298,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Maria Danvind</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115250546</v>
+        <v>115249895</v>
       </c>
       <c r="B27" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3532,37 +3328,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447017</v>
+        <v>447152</v>
       </c>
       <c r="R27" t="n">
-        <v>6919258</v>
+        <v>6918961</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3618,15 +3414,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115248063</v>
+        <v>115250834</v>
       </c>
       <c r="B28" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3634,34 +3425,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Smaldalen, Smaldalen, Hjd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447193</v>
+        <v>446949</v>
       </c>
       <c r="R28" t="n">
-        <v>6918846</v>
+        <v>6919364</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3720,50 +3511,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>115248009</v>
+        <v>115250401</v>
       </c>
       <c r="B29" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gammelnipan (Gammelnipan), Hjd</t>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447189</v>
+        <v>447049</v>
       </c>
       <c r="R29" t="n">
-        <v>6918832</v>
+        <v>6919190</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3822,15 +3608,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>115284876</v>
+        <v>115250546</v>
       </c>
       <c r="B30" t="n">
-        <v>77446</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3838,40 +3619,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>446952</v>
+        <v>447017</v>
       </c>
       <c r="R30" t="n">
-        <v>6919314</v>
+        <v>6919258</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3909,75 +3687,66 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115284995</v>
+        <v>115248081</v>
       </c>
       <c r="B31" t="n">
-        <v>78247</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6456</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447216</v>
+        <v>447193</v>
       </c>
       <c r="R31" t="n">
-        <v>6918856</v>
+        <v>6918846</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4015,34 +3784,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115284997</v>
+        <v>115248063</v>
       </c>
       <c r="B32" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4068,22 +3831,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447216</v>
+        <v>447193</v>
       </c>
       <c r="R32" t="n">
-        <v>6918856</v>
+        <v>6918846</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4121,62 +3881,55 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115284894</v>
+        <v>115284971</v>
       </c>
       <c r="B33" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4184,13 +3937,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447064</v>
+        <v>447166</v>
       </c>
       <c r="R33" t="n">
-        <v>6919117</v>
+        <v>6918954</v>
       </c>
       <c r="S33" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4228,6 +3981,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4246,15 +4000,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115284963</v>
+        <v>115284978</v>
       </c>
       <c r="B34" t="n">
-        <v>78157</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4262,21 +4011,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4289,10 +4038,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447133</v>
+        <v>447194</v>
       </c>
       <c r="R34" t="n">
-        <v>6919015</v>
+        <v>6918896</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4352,15 +4101,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>115284971</v>
+        <v>115284997</v>
       </c>
       <c r="B35" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4395,10 +4139,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447166</v>
+        <v>447216</v>
       </c>
       <c r="R35" t="n">
-        <v>6918954</v>
+        <v>6918856</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4458,56 +4202,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>115285005</v>
+        <v>115250672</v>
       </c>
       <c r="B36" t="n">
-        <v>90897</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>760</v>
+        <v>6464</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447189</v>
+        <v>447014</v>
       </c>
       <c r="R36" t="n">
-        <v>6918830</v>
+        <v>6919303</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4545,34 +4281,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Bjarne Tutturen</t>
+          <t>Maria Danvind</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>115284852</v>
+        <v>115284876</v>
       </c>
       <c r="B37" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4580,21 +4310,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229821</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4607,10 +4337,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>446885</v>
+        <v>446952</v>
       </c>
       <c r="R37" t="n">
-        <v>6919391</v>
+        <v>6919314</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4670,42 +4400,38 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>115284978</v>
+        <v>115284894</v>
       </c>
       <c r="B38" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4713,13 +4439,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447194</v>
+        <v>447064</v>
       </c>
       <c r="R38" t="n">
-        <v>6918896</v>
+        <v>6919117</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4757,7 +4483,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4776,56 +4501,55 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115284871</v>
+        <v>131293639</v>
       </c>
       <c r="B39" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103907</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>223284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Sälg</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gammelnipan, Hjd</t>
+          <t>Gammelnipa, Hjd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>446952</v>
+        <v>447126</v>
       </c>
       <c r="R39" t="n">
-        <v>6919314</v>
+        <v>6918761</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4847,14 +4571,24 @@
           <t>Vemdalen</t>
         </is>
       </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>ed544876-9f53-41bb-be48-0be86e10aad9</t>
+        </is>
+      </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gammal hamlad sälg</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4863,22 +4597,809 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
+          <t>Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Via Bodil Carlsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>115284995</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>447216</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6918856</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
           <t>Bjarne Tutturen</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
+      <c r="AX40" t="inlineStr">
         <is>
           <t>Bjarne Tutturen</t>
         </is>
       </c>
-      <c r="AY39" t="inlineStr"/>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>115248009</v>
+      </c>
+      <c r="B41" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>447189</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6918832</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>115248171</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>447166</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6918864</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>115250589</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>447016</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6919258</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>115250791</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Smaldalen, Smaldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>446966</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6919361</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115251041</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Smaldalen, Smaldalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>446882</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6919449</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115251592</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>447187</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6918950</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Maria Danvind</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>115284852</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Gammelnipan, Hjd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>446885</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6919391</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-03-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bjarne Tutturen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 8533-2024 artfynd.xlsx
+++ b/artfynd/A 8533-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81531</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104888</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316125</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316126</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316128</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316129</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316131</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316132</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1642,6 +1687,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316133</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1750,6 +1800,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316134</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1858,6 +1913,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316135</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1966,6 +2026,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316136</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2074,6 +2139,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316137</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2182,6 +2252,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/316138</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2288,6 +2363,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62064254</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2396,6 +2476,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/811798</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2504,6 +2589,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/811799</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2612,6 +2702,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1901591</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2720,6 +2815,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1887400</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2817,6 +2917,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59520431</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2914,6 +3019,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59520432</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3015,6 +3125,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284963</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3112,6 +3227,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115247963</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3213,6 +3333,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115285005</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3310,6 +3435,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115249895</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3407,6 +3537,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115250401</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3504,6 +3639,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115248081</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3601,6 +3741,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115248063</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3702,6 +3847,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284971</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3803,6 +3953,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284978</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3904,6 +4059,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284997</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4005,6 +4165,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284894</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4121,6 +4286,11 @@
       <c r="AY34" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131293639</t>
         </is>
       </c>
     </row>
@@ -4224,6 +4394,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284995</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4321,6 +4496,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115248009</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4418,6 +4598,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115248171</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4515,6 +4700,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115251592</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4616,6 +4806,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284871</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4713,6 +4908,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115250834</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4810,6 +5010,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115250546</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4907,6 +5112,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115250672</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5008,6 +5218,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284876</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5105,6 +5320,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115250589</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5202,6 +5422,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115250791</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5299,6 +5524,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115251041</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5400,8 +5630,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115284852</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>